--- a/data_extactor/batch_10_fa/batch_0022_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0022_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>نرم‌افزار Assistant Software for Antimicrobial Susceptibility Interpretation ASASI | BD Biosciences CellQuest | BD Biosciences CloneCyt | ابزار Basic Local Alignment Search Tool BLAST | Bruker Optics OPUS | نرم‌افزار BtB Software Mycobacteriology Lab | پایگاه داده Codon Usage Database | ComBase | سیستم آزمایشگاهی Computer Service &amp; Support CLS-2000 Laboratory System | سیستم مدیریت اطلاعات آزمایشگاهی Computing Solutions LabSoft LIMS Micro | بارنامه‌های DM2 | نرم‌افزار مدیریت پایگاه داده | نرم‌افزار ایمیل | FindTarget | FramePlot | Gene Finder | نرم‌افزار تشخیص ژن | Genie Interactive | نرم‌افزار ضبط و تحلیل تصویر | سیستم مدیریت اطلاعات آزمایشگاهی LIMS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | NetLims AutoLims | سیستم اطلاعات آزمایشگاهی Orchard Software Orchard Harvest LIS | PHYLIP | PIBWin | برنامه مدل‌سازی پاتوژن PMP | PredictProtein | Proscan | ProtScale | Protein Explorer | پایگاه‌های داده پروتئین | نرم‌افزار SAP | STARLIMS | نرم‌افزار آماری | TreeView | Verity Software House ModFit LT | WHONET | نرم‌افزار مرورگر وب</t>
+          <t>نرم‌افزار Assistant Software for Antimicrobial Susceptibility Interpretation ASASI | BD Biosciences CellQuest | BD Biosciences CloneCyt | ابزار Basic Local Alignment Search Tool BLAST | Bruker Optics OPUS | نرم‌افزار BtB Software Mycobacteriology Lab | پایگاه داده Codon Usage Database | ComBase | سیستم آزمایشگاهی Computer Service &amp; Support CLS-2000 Laboratory System | سیستم مدیریت اطلاعات آزمایشگاهی Computing Solutions LabSoft LIMS Micro | DM2 Bills of Lading | نرم‌افزار مدیریت پایگاه داده | نرم‌افزار ایمیل | FindTarget | FramePlot | Gene Finder | نرم‌افزار تشخیص ژن | Genie Interactive | نرم‌افزار ضبط و تحلیل تصویر | سیستم مدیریت اطلاعات آزمایشگاهی LIMS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | NetLims AutoLims | Orchard Software Orchard Harvest LIS | PHYLIP | PIBWin | برنامه مدل‌سازی پاتوژن PMP | PredictProtein | Proscan | ProtScale | Protein Explorer | پایگاه‌های داده پروتئین | نرم‌افزار SAP | STARLIMS | نرم‌افزار آماری | TreeView | Verity Software House ModFit LT | WHONET | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>علم | درک مطلب | تفکر انتقادی | نوشتن | گوش دادن فعال | صحبت کردن | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
+          <t>علوم | درک مطلب | تفکر انتقادی | نگارش | گوش دادن فعال | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | شیمی | زبان انگلیسی | کامپیوتر و الکترونیک | آموزش و پرورش | ریاضیات | مهندسی و فناوری</t>
+          <t>زیست‌شناسی | شیمی | زبان انگلیسی | رایانه و الکترونیک | آموزش و پرورش | ریاضیات | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک نوشتاری | بیان نوشتاری | استدلال استقرایی | حساسیت به مسئله | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | درک شنیداری | بیان شفاهی | نظم‌دهی اطلاعات | انعطاف‌پذیری بستار | دید نزدیک | روانی ایده‌ها | تشخیص گفتار | توجه انتخابی | اصالت | وضوح گفتار | تشخیص رنگ بصری | مهارت انگشتان | تجسم | سرعت ادراکی</t>
+          <t>درک کتبی | بیان کتبی | استدلال استقرایی | حساسیت به مسئله | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | درک شفاهی | بیان شفاهی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | بینایی نزدیک | روانی ایده‌ها | تشخیص گفتار | توجه انتخابی | اصالت | وضوح گفتار | تشخیص رنگ بصری | مهارت انگشتان | تجسم | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | محیط داخلی، دارای کنترل محیطی | بحث‌های رودررو با افراد و درون تیم‌ها | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا صحیح بودن | مکالمات تلفنی | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | در معرض بیماری یا عفونت | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | در معرض آلاینده‌ها | پیامد خطا | تماس با دیگران | اهمیت تکرار وظایف مشابه | تأثیر تصمیمات بر همکاران یا نتایج شرکت | در معرض شرایط خطرناک | تناوب تصمیم‌گیری</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | مکالمات تلفنی | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض آلاینده‌ها | پیامد خطا | ارتباط با دیگران | اهمیت تکرار وظایف یکسان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض شرایط خطرناک | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تکنیسین‌های کشاورزی | بیوشیمی‌دان‌ها و بیوفیزیک‌دان‌ها | مهندسان زیستی و مهندسان زیست‌پزشکی | دانشمندان بیوانفورماتیک | تکنیسین‌های زیستی | زیست‌شناسان | تکنیسین‌های شیمی | شیمی‌دان‌ها | تکنولوژیست‌های سیتوژنتیک | اپیدمیولوژیست‌ها | ژنتیک‌دان‌ها | تکنیسین‌های بافت‌شناسی | هیستوتکنولوژیست‌ها | دانشمندان پزشکی، به جز اپیدمیولوژیست‌ها | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | زیست‌شناسان مولکولی و سلولی | تکنولوژیست‌ها و تکنیسین‌های مهندسی نانوتکنولوژی | پزشکان، آسیب‌شناسان | دانشمندان خاک و گیاه</t>
+          <t>تکنسین‌های کشاورزی | بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان زیستی و مهندسان زیست‌پزشکی | دانشمندان بیوانفورماتیک | تکنسین‌های زیستی | زیست‌شناسان | تکنسین‌های شیمی | شیمی‌دانان | تکنولوژیست‌های سیتوژنتیک | اپیدمیولوژیست‌ها | ژنتیک‌دان‌ها | تکنیسین‌های هیستولوژی | هیستوتکنولوژیست‌ها | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | زیست‌شناسان مولکولی و سلولی | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | پزشکان، آسیب‌شناسان | دانشمندان خاک و گیاه</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,12 +560,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>نرم‌افزار مدل‌سازی کامپیوتری | مجموعه اداری Corel WordPerfect Office Suite | نرم‌افزار مدیریت پایگاه داده | نرم‌افزار ESRI ArcGIS | ESRI ArcView | نرم‌افزار ایمیل | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | HATPRO | IBM Lotus 1-2-3 | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Python | R | نرم‌افزار پایگاه داده رابطه‌ای | SAS | نرم‌افزار Salesforce | نرم‌افزار آماری | نرم‌افزار مرورگر وب</t>
+          <t>نرم‌افزار مدل‌سازی کامپیوتری | Corel WordPerfect Office Suite | نرم‌افزار مدیریت پایگاه داده | نرم‌افزار ESRI ArcGIS | ESRI ArcView | نرم‌افزار ایمیل | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | HATPRO | IBM Lotus 1-2-3 | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Python | R | نرم‌افزار پایگاه داده رابطه‌ای | SAS | نرم‌افزار Salesforce | نرم‌افزار آماری | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | صحبت کردن | گوش دادن فعال | درک مطلب | نوشتن | علم | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | علوم | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,17 +575,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | درک شنیداری | درک نوشتاری | وضوح گفتار | نظم‌دهی اطلاعات | حساسیت به مسئله | تشخیص گفتار | دید نزدیک | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | انعطاف‌پذیری بستار | اشتراک زمانی | سرعت ادراکی | تسهیلات عددی | استدلال ریاضی | دید دور</t>
+          <t>بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | وضوح گفتار | ترتیب‌دهی اطلاعات | حساسیت به مسئله | تشخیص گفتار | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | انعطاف‌پذیری بستار | تقسیم توجه | سرعت ادراکی | توانایی عددی | استدلال ریاضی | بینایی دور</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل محیطی | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا صحیح بودن | آزادی در تصمیم‌گیری | نتایج کاری و خروجی‌های سایر کارکنان | تعامل با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تناوب تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | صرف زمان برای نشستن | در وسیله نقلیه محصور یا کار با تجهیزات محصور</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | تعامل با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | صرف زمان برای نشستن | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>معلمان علوم کشاورزی، پس از متوسطه | تکنیسین‌های کشاورزی | دانشمندان علوم دامی | تکنیسین‌های زیستی | زیست‌شناسان | دانشمندان حفاظت | برنامه‌ریزان احیای محیط زیست | معلمان علوم محیطی، پس از متوسطه | دانشمندان و متخصصان محیط زیست، شامل بهداشت | محیط‌بانان ماهی و شکار | تکنیسین‌های جنگل و حفاظت | کارکنان جنگل و حفاظت | جنگل‌بانان | معلمان علوم جنگلداری و حفاظت، پس از متوسطه | زمین‌شناسان، به جز هیدرولوژیست‌ها و جغرافیدان‌ها | هیدرولوژیست‌ها | اکولوژیست‌های صنعتی | میکروبیولوژیست‌ها | مدیران مراتع | دانشمندان خاک و گیاه</t>
+          <t>مدرسان علوم کشاورزی، پس از متوسطه | تکنسین‌های کشاورزی | دانشمندان علوم دامی | تکنسین‌های زیستی | زیست‌شناسان | دانشمندان حفاظت | برنامه‌ریزان احیای محیط‌زیست | مدرسان علوم محیطی، پس از متوسطه | دانشمندان و متخصصان محیط زیست، شامل بهداشت | محیط‌بانان و جنگل‌بانان | تکنسین‌های جنگل و حفاظت | کارگران جنگل و حفاظت | جنگل‌بانان | مدرسان علوم جنگلداری و حفاظت، پس از متوسطه | زمین‌شناسان، به‌جز آب‌شناسان و جغرافی‌دانان | آب‌شناسان | بوم‌شناسان صنعتی | میکروبیولوژیست‌ها | مدیران مراتع | دانشمندان خاک و گیاه</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نوشتن | صحبت کردن | گوش دادن فعال | علم | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | شیمی | ریاضیات | زبان انگلیسی | کامپیوتر و الکترونیک | آموزش و پرورش | فیزیک | مدیریت و اداره | پزشکی و دندانپزشکی</t>
+          <t>زیست‌شناسی | شیمی | ریاضیات | زبان انگلیسی | رایانه و الکترونیک | آموزش و پرورش | فیزیک | مدیریت و اداره | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | اشتراک زمانی | تجسم | حفظ کردن | استدلال ریاضی | تسهیلات عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | صرف زمان برای نشستن | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | فشار زمانی | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | در معرض شرایط خطرناک | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | پیامد خطا | اهمیت تکرار وظایف مشابه</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض شرایط خطرناک | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | پیامد خطا | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>جانورشناسان و زیست‌شناسان حیات وحش | میکروبیولوژیست‌ها | بیوشیمی‌دان‌ها و بیوفیزیک‌دان‌ها | زیست‌شناسان مولکولی و سلولی | ژنتیک‌دان‌ها | زیست‌شناسان | دانشمندان بیوانفورماتیک | دانشمندان علوم دامی | دانشمندان خاک و گیاه | دانشمندان و تکنولوژیست‌های مواد غذایی | دانشمندان پزشکی، به جز اپیدمیولوژیست‌ها | اپیدمیولوژیست‌ها | دانشمندان حفاظت | جنگل‌بانان | دانشمندان و متخصصان محیط زیست، شامل بهداشت | تکنیسین‌های زیستی | معلمان علوم زیستی، پس از متوسطه | مدیران علوم طبیعی | مدیران مراتع | طبیعت‌شناسان پارک</t>
+          <t>جانورشناسان و زیست‌شناسان حیات وحش | میکروبیولوژیست‌ها | بیوشیمی‌دانان و بیوفیزیک‌دانان | زیست‌شناسان مولکولی و سلولی | ژنتیک‌دان‌ها | زیست‌شناسان | دانشمندان بیوانفورماتیک | دانشمندان علوم دامی | دانشمندان خاک و گیاه | دانشمندان و تکنولوژیست‌های علوم غذایی | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | اپیدمیولوژیست‌ها | دانشمندان حفاظت | جنگل‌بانان | دانشمندان و متخصصان محیط زیست، شامل بهداشت | تکنسین‌های زیستی | مدرسان علوم زیستی، پس از متوسطه | مدیران علوم طبیعی | مدیران مراتع | طبیعت‌شناسان پارک</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Accelrys Pipeline Pilot | نرم‌افزار Amazon Web Services AWS | Apache Accumulo | Apache Groovy | Apache HTTP Server | Apache Hadoop | BLAT | BWA | Bash | BioPerl | Bioconductor | نرم‌افزار Bioconductor | Biomatters Geneious | Bowtie | C | C# | C++ | Canu | ClustalW | Cufflinks | Cytel StatXact | نرم‌افزار توالی‌یابی DNA | نرم‌افزار تجسم داده‌ها | Django | Docker | ENSEMBL | زبان نشانه‌گذاری توسعه‌پذیر XML | ترجمه فرمول FORTRAN | GenBank | GenePattern | Genedata Expressionist | ابزار Genome Analysis Toolkit GATK | Git | GitHub | زبان نشانه‌گذاری ابرمتنی HTML | IBM SPSS Statistics | سیستم مدیریت اطلاعات آزمایشگاهی Illumina LIMS | JavaScript | نشان‌گذاری شیء جاوا اسکریپت JSON | Life Technologies SOLiD | Life Technologies Vector NTI | Linux | Microsoft Access | Microsoft Active Server Pages ASP | نرم‌افزار Microsoft Azure | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft SQL Server | سرویس‌های گزارش‌دهی Microsoft SQL Server SSRS | Microsoft SharePoint | Microsoft Visual Basic for Applications VBA | Microsoft Visual Studio | MySQL | NCBI RefSeq | NoSQL | نرم‌افزار محیط توسعه شیءگرا | Oracle Database | Oracle Java | صفحات سرور جاوا اوراکل JSP | Oracle PL/SQL | PHP | Perl | PostgreSQL | Primer3 | پایگاه‌های داده ژنومیک عمومی | Python | R | نرم‌افزار توالی‌یابی RNA | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | Roche 454 Life Sciences GS Data Analysis | Ruby | نرم‌افزار SAP | SAS | نرم‌افزار Salesforce | Scala | اسکریپت Shell | Snakemake | ابزارهای توسعه نرم‌افزار | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | TIBCO Spotfire S+ | Tableau | نرم‌افزار Teradata | The MathWorks MATLAB | Tibco S-PLUS | TopHat | UNIX | نرم‌افزار طراحی رابط کاربری | Velvet | نرم‌افزار مرورگر وب | dbSNP | jQuery</t>
+          <t>Accelrys Pipeline Pilot | نرم‌افزار Amazon Web Services AWS | Apache Accumulo | Apache Groovy | Apache HTTP Server | Apache Hadoop | BLAT | BWA | Bash | BioPerl | Bioconductor | نرم‌افزار Bioconductor | Biomatters Geneious | Bowtie | C | C# | C++ | Canu | ClustalW | Cufflinks | Cytel StatXact | نرم‌افزار توالی‌یابی DNA | نرم‌افزار تجسم داده | Django | Docker | ENSEMBL | زبان نشانه‌گذاری توسعه‌پذیر XML | Formula translation/translator FORTRAN | GenBank | GenePattern | Genedata Expressionist | Genome Analysis Toolkit GATK | Git | GitHub | زبان نشانه‌گذاری ابرمتن HTML | IBM SPSS Statistics | سیستم مدیریت اطلاعات آزمایشگاهی Illumina LIMS | JavaScript | JavaScript Object Notation JSON | Life Technologies SOLiD | Life Technologies Vector NTI | Linux | Microsoft Access | Microsoft Active Server Pages ASP | نرم‌افزار Microsoft Azure | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft SQL Server | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Visual Basic for Applications VBA | Microsoft Visual Studio | MySQL | NCBI RefSeq | NoSQL | نرم‌افزار محیط توسعه شیءگرا | Oracle Database | Oracle Java | Oracle JavaServer Pages JSP | Oracle PL/SQL | PHP | Perl | PostgreSQL | Primer3 | پایگاه‌های داده ژنومیک عمومی | Python | R | نرم‌افزار توالی‌یابی RNA | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | Roche 454 Life Sciences GS Data Analysis | Ruby | نرم‌افزار SAP | SAS | نرم‌افزار Salesforce | Scala | Shell script | Snakemake | ابزارهای توسعه نرم‌افزار | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | TIBCO Spotfire S+ | Tableau | نرم‌افزار Teradata | The MathWorks MATLAB | Tibco S-PLUS | TopHat | UNIX | نرم‌افزار طراحی رابط کاربری | Velvet | نرم‌افزار مرورگر وب | dbSNP | jQuery</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | صحبت کردن | گوش دادن فعال | نوشتن | علم | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | درک مطلب | سخن گفتن | گوش دادن فعال | نگارش | علوم | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | کامپیوتر و الکترونیک | ریاضیات | زبان انگلیسی | شیمی | آموزش و پرورش | اداری</t>
+          <t>زیست‌شناسی | رایانه و الکترونیک | ریاضیات | زبان انگلیسی | شیمی | آموزش و پرورش | اداری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان نوشتاری | درک نوشتاری | درک شنیداری | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | روانی ایده‌ها | استدلال ریاضی | اصالت | انعطاف‌پذیری دسته‌بندی | دید نزدیک | تسهیلات عددی | وضوح گفتار | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری بستار | دید دور | سرعت ادراکی | حفظ کردن</t>
+          <t>بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | استدلال ریاضی | اصالت | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | توانایی عددی | وضوح گفتار | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری بستار | بینایی دور | سرعت ادراکی | حفظ کردن</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | صرف زمان برای نشستن | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل محیطی | اهمیت دقیق یا صحیح بودن | مکالمات تلفنی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت | نتایج کاری و خروجی‌های سایر کارکنان | تماس با دیگران</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای نشستن | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | مکالمات تلفنی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت | پیامدهای کاری و نتایج سایر کارکنان | ارتباط با دیگران</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>بیوشیمی‌دان‌ها و بیوفیزیک‌دان‌ها | مهندسان زیستی و مهندسان زیست‌پزشکی | تکنیسین‌های بیوانفورماتیک | معلمان علوم زیستی، پس از متوسطه | تکنیسین‌های زیستی | بیواستاتیست‌ها | مدیران داده‌های بالینی | تکنولوژیست‌های سیتوژنتیک | دانشمندان داده | ژنتیک‌دان‌ها | ریاضی‌دان‌ها | دانشمندان پزشکی، به جز اپیدمیولوژیست‌ها | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | زیست‌شناسان مولکولی و سلولی | مهندسان نانوسیستم‌ها | تکنولوژیست‌ها و تکنیسین‌های مهندسی نانوتکنولوژی | مدیران علوم طبیعی | توسعه‌دهندگان نرم‌افزار | آماردان‌ها</t>
+          <t>بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان زیستی و مهندسان زیست‌پزشکی | تکنسین‌های بیوانفورماتیک | مدرسان علوم زیستی، پس از متوسطه | تکنسین‌های زیستی | آمارشناسان زیستی | مدیران داده‌های بالینی | تکنولوژیست‌های سیتوژنتیک | دانشمندان داده | ژنتیک‌دان‌ها | ریاضی‌دانان | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | زیست‌شناسان مولکولی و سلولی | مهندسان نانوسیستم | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | مدیران علوم طبیعی | توسعه‌دهندگان نرم‌افزار | آمارشناسان</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AcaClone pDRAW32 | Adobe Illustrator | Agilent CGH Analytics | Agilent Technologies GeneSpring GX | ابزار Basic Local Alignment Search Tool BLAST | Blast Output Browser BOB | C++ | CRI-MAP | ClustalW | Corel CorelDraw Graphics Suite | مجموعه اداری Corel WordPerfect Office Suite | Delila | کتابخانه‌های اسید دئوکسی‌ریبونوکلئیک DNA | EnzymeX | FASTA | FASTLINK | Gene Recognition and Assembly Internet Link GRAIL | نرم‌افزار ژنوتیپ‌بندی | Geospiza GeneSifter | Git | GraphPad Software GraphPad Prism | سیستم مدیریت اطلاعات آزمایشگاهی LIMS | نرم‌افزار Magma Design Automation | Mathsoft Mathcad | Mendel | Michigan State University MSU ProFlex | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | Minitab | Molecular Devices Corporation MetaMorph | NetPrimer | PHYLIP | Primer3 | Python | R | RasMol | Textco BioSoftware Gene Inspector | The MathWorks MATLAB | نرم‌افزار مرورگر وب | Wolfram Research Mathematica</t>
+          <t>AcaClone pDRAW32 | Adobe Illustrator | Agilent CGH Analytics | Agilent Technologies GeneSpring GX | ابزار Basic Local Alignment Search Tool BLAST | Blast Output Browser BOB | C++ | CRI-MAP | ClustalW | Corel CorelDraw Graphics Suite | Corel WordPerfect Office Suite | Delila | کتابخانه‌های اسید دئوکسی‌ریبونوکلئیک DNA | EnzymeX | FASTA | FASTLINK | Gene Recognition and Assembly Internet Link GRAIL | نرم‌افزار ژنوتیپ‌بندی | Geospiza GeneSifter | Git | GraphPad Software GraphPad Prism | سیستم مدیریت اطلاعات آزمایشگاهی LIMS | نرم‌افزار Magma Design Automation | Mathsoft Mathcad | Mendel | Michigan State University MSU ProFlex | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | Minitab | Molecular Devices Corporation MetaMorph | NetPrimer | PHYLIP | Primer3 | Python | R | RasMol | Textco BioSoftware Gene Inspector | The MathWorks MATLAB | نرم‌افزار مرورگر وب | Wolfram Research Mathematica</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>علم | درک مطلب | نوشتن | تفکر انتقادی | صحبت کردن | گوش دادن فعال | یادگیری فعال | راهبردهای یادگیری | ریاضیات | نظارت</t>
+          <t>علوم | درک مطلب | نگارش | تفکر انتقادی | سخن گفتن | گوش دادن فعال | یادگیری فعال | راهبردهای یادگیری | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | زبان انگلیسی | شیمی | ریاضیات | آموزش و پرورش | کامپیوتر و الکترونیک | پزشکی و دندانپزشکی</t>
+          <t>زیست‌شناسی | زبان انگلیسی | شیمی | ریاضیات | آموزش و پرورش | رایانه و الکترونیک | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک نوشتاری | درک شنیداری | بیان شفاهی | بیان نوشتاری | استدلال استقرایی | حساسیت به مسئله | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات | استدلال ریاضی | روانی ایده‌ها | دید نزدیک | وضوح گفتار | اصالت | تشخیص گفتار | تسهیلات عددی | انعطاف‌پذیری بستار | توجه انتخابی | دید دور | سرعت ادراکی | سرعت بستار | تشخیص رنگ بصری</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | استدلال استقرایی | حساسیت به مسئله | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال ریاضی | روانی ایده‌ها | بینایی نزدیک | وضوح گفتار | اصالت | تشخیص گفتار | توانایی عددی | انعطاف‌پذیری بستار | توجه انتخابی | بینایی دور | سرعت ادراکی | سرعت بستار | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | محیط داخلی، دارای کنترل محیطی | بحث‌های رودررو با افراد و درون تیم‌ها | اهمیت دقیق یا صحیح بودن | سطح رقابت | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | تماس با دیگران | صرف زمان برای نشستن</t>
+          <t>ایمیل | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | سطح رقابت | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>بیوشیمی‌دان‌ها و بیوفیزیک‌دان‌ها | مهندسان زیستی و مهندسان زیست‌پزشکی | دانشمندان بیوانفورماتیک | تکنیسین‌های بیوانفورماتیک | معلمان علوم زیستی، پس از متوسطه | تکنیسین‌های زیستی | زیست‌شناسان | معلمان شیمی، پس از متوسطه | شیمی‌دان‌ها | تکنولوژیست‌های سیتوژنتیک | ژنتیک‌دان‌ها | هیستوتکنولوژیست‌ها | دانشمندان پزشکی، به جز اپیدمیولوژیست‌ها | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | مهندسان نانوسیستم‌ها | تکنولوژیست‌ها و تکنیسین‌های مهندسی نانوتکنولوژی | مدیران علوم طبیعی | پزشکان، آسیب‌شناسان</t>
+          <t>بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان زیستی و مهندسان زیست‌پزشکی | دانشمندان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | مدرسان علوم زیستی، پس از متوسطه | تکنسین‌های زیستی | زیست‌شناسان | مدرسان شیمی، پس از متوسطه | شیمی‌دانان | تکنولوژیست‌های سیتوژنتیک | ژنتیک‌دان‌ها | هیستوتکنولوژیست‌ها | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | مهندسان نانوسیستم | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | مدیران علوم طبیعی | پزشکان، آسیب‌شناسان</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ابزار Basic Local Alignment Search Tool BLAST | پایگاه‌های داده بیوانفورماتیک | C++ | ClustalW | نرم‌افزار پایگاه داده | نرم‌افزار تحلیل توالی اسید دئوکسی‌ریبونوکلئیک DNA | نرم‌افزار ایمیل | ترجمه فرمول FORTRAN | Git | GitHub | Golden Helix HelixTree | HapMap | Insightful S-PLUS | Linux | Mendel | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Visual C# .NET | Microsoft Word | Oracle Java | PHYLIP | Perl | نرم‌افزار دستگاه خوانش پلیت | Python | R | RTI International SUDAAN | SAS | SAS JMP | SAS/Genetics | نرم‌افزار حسابداری Sage | زبان پرس‌وجوی ساختاریافته SQL | UNIX | Ward Systems Group GeneHunter | نرم‌افزار مرورگر وب</t>
+          <t>ابزار Basic Local Alignment Search Tool BLAST | پایگاه‌های داده بیوانفورماتیک | C++ | ClustalW | نرم‌افزار پایگاه داده | نرم‌افزار تحلیل توالی اسید دئوکسی‌ریبونوکلئیک DNA | نرم‌افزار ایمیل | Formula translation/translator FORTRAN | Git | GitHub | Golden Helix HelixTree | HapMap | Insightful S-PLUS | Linux | Mendel | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Visual C# .NET | Microsoft Word | Oracle Java | PHYLIP | Perl | نرم‌افزار دستگاه خوانش پلیت | Python | R | RTI International SUDAAN | SAS | SAS JMP | SAS/Genetics | نرم‌افزار حسابداری Sage | زبان پرس‌وجوی ساختاریافته SQL | UNIX | Ward Systems Group GeneHunter | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | علم | یادگیری فعال | تفکر انتقادی | صحبت کردن | نوشتن | گوش دادن فعال | ریاضیات | راهبردهای یادگیری | نظارت</t>
+          <t>درک مطلب | علوم | یادگیری فعال | تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال | ریاضیات | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | زبان انگلیسی | آموزش و پرورش | ریاضیات | شیمی | کامپیوتر و الکترونیک</t>
+          <t>زیست‌شناسی | زبان انگلیسی | آموزش و پرورش | ریاضیات | شیمی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک نوشتاری | بیان نوشتاری | استدلال استقرایی | بیان شفاهی | درک شنیداری | حساسیت به مسئله | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات | استدلال ریاضی | روانی ایده‌ها | دید نزدیک | وضوح گفتار | اصالت | تسهیلات عددی | انعطاف‌پذیری بستار | تشخیص گفتار | توجه انتخابی | دید دور</t>
+          <t>درک کتبی | بیان کتبی | استدلال استقرایی | بیان شفاهی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال ریاضی | روانی ایده‌ها | بینایی نزدیک | وضوح گفتار | اصالت | توانایی عددی | انعطاف‌پذیری بستار | تشخیص گفتار | توجه انتخابی | بینایی دور</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | محیط داخلی، دارای کنترل محیطی | آزادی در تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | بحث‌های رودررو با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | سطح رقابت | کار با یا مشارکت در یک گروه کاری یا تیم | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | تماس با دیگران</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | سطح رقابت | کار با یا مشارکت در یک گروه کاری یا تیم | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | ارتباط با دیگران</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>بیوشیمی‌دان‌ها و بیوفیزیک‌دان‌ها | مهندسان زیستی و مهندسان زیست‌پزشکی | دانشمندان بیوانفورماتیک | تکنیسین‌های بیوانفورماتیک | معلمان علوم زیستی، پس از متوسطه | تکنیسین‌های زیستی | زیست‌شناسان | بیواستاتیست‌ها | هماهنگ‌کنندگان پژوهش‌های بالینی | تکنولوژیست‌های سیتوژنتیک | دانشمندان داده | اپیدمیولوژیست‌ها | مشاوران ژنتیک | دانشمندان پزشکی، به جز اپیدمیولوژیست‌ها | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | زیست‌شناسان مولکولی و سلولی | پزشکان، آسیب‌شناسان | آماردان‌ها</t>
+          <t>بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان زیستی و مهندسان زیست‌پزشکی | دانشمندان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | مدرسان علوم زیستی، پس از متوسطه | تکنسین‌های زیستی | زیست‌شناسان | آمارشناسان زیستی | هماهنگ‌کنندگان تحقیقات بالینی | تکنولوژیست‌های سیتوژنتیک | دانشمندان داده | اپیدمیولوژیست‌ها | مشاوران ژنتیک | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | زیست‌شناسان مولکولی و سلولی | پزشکان، آسیب‌شناسان | آمارشناسان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>علم | درک مطلب | نوشتن | گوش دادن فعال | تفکر انتقادی | صحبت کردن | ریاضیات | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
+          <t>علوم | درک مطلب | نگارش | گوش دادن فعال | تفکر انتقادی | سخن گفتن | ریاضیات | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان نوشتاری | استدلال استقرایی | دید نزدیک | بیان شفاهی | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | روانی ایده‌ها | انعطاف‌پذیری بستار | دید دور | تسهیلات عددی | اصالت | تجسم | سرعت ادراکی | تشخیص رنگ بصری | توجه انتخابی</t>
+          <t>درک شفاهی | درک کتبی | بیان کتبی | استدلال استقرایی | بینایی نزدیک | بیان شفاهی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | روانی ایده‌ها | انعطاف‌پذیری بستار | بینایی دور | توانایی عددی | اصالت | تجسم | سرعت ادراکی | تشخیص رنگ بصری | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ایمیل | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | بحث‌های رودررو با افراد و درون تیم‌ها | سطح رقابت | تماس با دیگران | نتایج کاری و خروجی‌های سایر کارکنان | محیط داخلی، دارای کنترل محیطی | مکالمات تلفنی | صرف زمان برای نشستن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا صحیح بودن</t>
+          <t>ایمیل | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سطح رقابت | ارتباط با دیگران | پیامدهای کاری و نتایج سایر کارکنان | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | صرف زمان برای نشستن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا درست بودن</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>بیوشیمی‌دان‌ها و بیوفیزیک‌دان‌ها | مهندسان زیستی و مهندسان زیست‌پزشکی | دانشمندان بیوانفورماتیک | معلمان علوم زیستی، پس از متوسطه | تکنیسین‌های زیستی | دانشمندان حفاظت | برنامه‌ریزان احیای محیط زیست | معلمان علوم محیطی، پس از متوسطه | دانشمندان و متخصصان محیط زیست، شامل بهداشت | معلمان علوم جنگلداری و حفاظت، پس از متوسطه | ژنتیک‌دان‌ها | زمین‌شناسان، به جز هیدرولوژیست‌ها و جغرافیدان‌ها | اکولوژیست‌های صنعتی | دانشمندان پزشکی، به جز اپیدمیولوژیست‌ها | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | زیست‌شناسان مولکولی و سلولی | مدیران علوم طبیعی | دانشمندان خاک و گیاه | جانورشناسان و زیست‌شناسان حیات وحش</t>
+          <t>بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان زیستی و مهندسان زیست‌پزشکی | دانشمندان بیوانفورماتیک | مدرسان علوم زیستی، پس از متوسطه | تکنسین‌های زیستی | دانشمندان حفاظت | برنامه‌ریزان احیای محیط‌زیست | مدرسان علوم محیطی، پس از متوسطه | دانشمندان و متخصصان محیط زیست، شامل بهداشت | مدرسان علوم جنگلداری و حفاظت، پس از متوسطه | ژنتیک‌دان‌ها | زمین‌شناسان، به‌جز آب‌شناسان و جغرافی‌دانان | بوم‌شناسان صنعتی | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | زیست‌شناسان مولکولی و سلولی | مدیران علوم طبیعی | دانشمندان خاک و گیاه | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,32 +902,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Autodesk AutoCAD | Autodesk Maya | Clover Technology GALENA | CroPMan | CropSyst Suite | Datasurge GEOPRO | Delft GeoSystems MStab | نرم‌افزار ESRI ArcGIS | ESRI ArcInfo | ESRI ArcView | نرم‌افزار ایمیل | GEO-SLOPE SEEP/W | GFA2D | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | HYDRUS-2D | Interstudio Geo-Tec B | سیستم مدیریت چشم‌انداز LMS | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Mitre Software GSLOPE | Salix Applied Earthcare Erosion Draw | پایگاه داده State Soil Geographic STATSGO | استودیوی مدل‌های تحلیلی STANMOD | U.S. Department of Agriculture USDA WinSRM | USDA Forest Vegetation Simulator FVS | سیستم پشتیبانی تصمیم‌گیری آب، خاک و هیدرومحیطی WATERSHEDSS | پایگاه‌های داده منابع آب | نرم‌افزار مرورگر وب | WinEPIC</t>
+          <t>Adobe Acrobat | Autodesk AutoCAD | Autodesk Maya | Clover Technology GALENA | CroPMan | CropSyst Suite | Datasurge GEOPRO | Delft GeoSystems MStab | نرم‌افزار ESRI ArcGIS | ESRI ArcInfo | ESRI ArcView | نرم‌افزار ایمیل | GEO-SLOPE SEEP/W | GFA2D | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | HYDRUS-2D | Interstudio Geo-Tec B | سیستم مدیریت چشم‌انداز LMS | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Mitre Software GSLOPE | Salix Applied Earthcare Erosion Draw | پایگاه داده جغرافیایی خاک ایالتی STATSGO | استودیوی مدل‌های تحلیلی STANMOD | U.S. Department of Agriculture USDA WinSRM | USDA Forest Vegetation Simulator FVS | سیستم پشتیبانی تصمیم‌گیری آب، خاک و هیدرومحیطی WATERSHEDSS | پایگاه‌های داده منابع آب | نرم‌افزار مرورگر وب | WinEPIC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | صحبت کردن | نوشتن | علم | تفکر انتقادی | نظارت | یادگیری فعال | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | علوم | تفکر انتقادی | نظارت | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | زیست‌شناسی | جغرافیا | ریاضیات | خدمات مشتری و شخصی | شیمی | قانون و دولت | کامپیوتر و الکترونیک | مهندسی و فناوری | آموزش و پرورش | طراحی | فیزیک | مدیریت و اداره</t>
+          <t>زبان انگلیسی | زیست‌شناسی | جغرافیا | ریاضیات | خدمات مشتری و شخصی | شیمی | قانون و دولت | رایانه و الکترونیک | مهندسی و فناوری | آموزش و پرورش | طراحی | فیزیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | نظم‌دهی اطلاعات | بیان نوشتاری | استدلال استقرایی | وضوح گفتار | انعطاف‌پذیری بستار | دید نزدیک | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | استدلال ریاضی | تسهیلات عددی | دید دور | سرعت ادراکی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | بیان کتبی | استدلال استقرایی | وضوح گفتار | انعطاف‌پذیری بستار | بینایی نزدیک | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | استدلال ریاضی | توانایی عددی | بینایی دور | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | در وسیله نقلیه محصور یا کار با تجهیزات محصور | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | فضای باز، در معرض تمام شرایط آب و هوایی | تعامل با مشتریان خارجی یا عموم مردم | محیط داخلی، دارای کنترل محیطی | اهمیت دقیق یا صحیح بودن | نامه‌ها و یادداشت‌های نوشتاری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | فضای باز، در معرض تمام شرایط آب و هوایی | تعامل با مشتریان خارجی یا عموم مردم | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | نامه‌ها و یادداشت‌های کتبی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | زیست‌شناسان | متخصصان بازسازی زمین‌های قهوه‌ای و مدیران سایت | بازرسان انطباق زیست‌محیطی | مهندسان محیط زیست | برنامه‌ریزان احیای محیط زیست | تکنیسین‌های علم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | تکنیسین‌های جنگل و حفاظت | جنگل‌بانان | زمین‌شناسان، به جز هیدرولوژیست‌ها و جغرافیدان‌ها | تکنیسین‌های هیدرولوژی | هیدرولوژیست‌ها | اکولوژیست‌های صنعتی | طبیعت‌شناسان پارک | مدیران مراتع | دانشمندان خاک و گیاه | متخصصان منابع آب | مهندسان آب/فاضلاب | جانورشناسان و زیست‌شناسان حیات وحش</t>
+          <t>مهندسان کشاورزی | زیست‌شناسان | متخصصان بازآفرینی زمین‌های قهوه‌ای و مدیران سایت | بازرسان انطباق زیست‌محیطی | مهندسان محیط زیست | برنامه‌ریزان احیای محیط‌زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | تکنسین‌های جنگل و حفاظت | جنگل‌بانان | زمین‌شناسان، به‌جز آب‌شناسان و جغرافی‌دانان | تکنسین‌های هیدرولوژی | آب‌شناسان | بوم‌شناسان صنعتی | طبیعت‌شناسان پارک | مدیران مراتع | دانشمندان خاک و گیاه | متخصصان منابع آب | مهندسان آب و فاضلاب | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب | صحبت کردن | تفکر انتقادی | نظارت | یادگیری فعال | نوشتن</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | زبان انگلیسی | جغرافیا | قانون و دولت | مدیریت و اداره | اداری | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | کامپیوتر و الکترونیک | آموزش و پرورش | ریاضیات | طراحی</t>
+          <t>زیست‌شناسی | زبان انگلیسی | جغرافیا | قانون و دولت | مدیریت و اداره | اداری | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | رایانه و الکترونیک | آموزش و پرورش | ریاضیات | طراحی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک نوشتاری | بیان شفاهی | درک شنیداری | بیان نوشتاری | حساسیت به مسئله | استدلال استقرایی | استدلال قیاسی | دید نزدیک | وضوح گفتار | تشخیص گفتار | دید دور | نظم‌دهی اطلاعات | روانی ایده‌ها | اصالت | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | انعطاف‌پذیری بستار | استدلال ریاضی</t>
+          <t>درک کتبی | بیان شفاهی | درک شفاهی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | استدلال قیاسی | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | بینایی دور | ترتیب‌دهی اطلاعات | روانی ایده‌ها | اصالت | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | انعطاف‌پذیری بستار | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | تماس با دیگران | تعامل با مشتریان خارجی یا عموم مردم | محیط داخلی، دارای کنترل محیطی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | در وسیله نقلیه محصور یا کار با تجهیزات محصور | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فضای باز، در معرض تمام شرایط آب و هوایی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای نشستن | نامه‌ها و یادداشت‌های نوشتاری | سلامت و ایمنی سایر کارکنان</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فضای باز، در معرض تمام شرایط آب و هوایی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای نشستن | نامه‌ها و یادداشت‌های کتبی | سلامت و ایمنی سایر کارکنان</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | زیست‌شناسان | متخصصان بازسازی زمین‌های قهوه‌ای و مدیران سایت | مدیران ارشد پایداری | دانشمندان حفاظت | مهندسان محیط زیست | برنامه‌ریزان احیای محیط زیست | دانشمندان و متخصصان محیط زیست، شامل بهداشت | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگلداری | محیط‌بانان ماهی و شکار | بازرسان و متخصصان پیشگیری از آتش‌سوزی جنگل | تکنیسین‌های جنگل و حفاظت | کارکنان جنگل و حفاظت | جنگل‌بانان | تکنیسین‌های هیدرولوژی | اکولوژیست‌های صنعتی | طبیعت‌شناسان پارک | دانشمندان خاک و گیاه | متخصصان منابع آب | جانورشناسان و زیست‌شناسان حیات وحش</t>
+          <t>مهندسان کشاورزی | زیست‌شناسان | متخصصان بازآفرینی زمین‌های قهوه‌ای و مدیران سایت | مدیران ارشد پایداری | دانشمندان حفاظت | مهندسان محیط زیست | برنامه‌ریزان احیای محیط‌زیست | دانشمندان و متخصصان محیط زیست، شامل بهداشت | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | محیط‌بانان و جنگل‌بانان | بازرسان و متخصصان پیشگیری از آتش‌سوزی جنگل | تکنسین‌های جنگل و حفاظت | کارگران جنگل و حفاظت | جنگل‌بانان | تکنسین‌های هیدرولوژی | بوم‌شناسان صنعتی | طبیعت‌شناسان پارک | دانشمندان خاک و گیاه | متخصصان منابع آب | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>صحبت کردن | درک مطلب | گوش دادن فعال | نوشتن | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | درک شنیداری | تشخیص گفتار | درک نوشتاری | بیان نوشتاری | استدلال قیاسی | حساسیت به مسئله | دید نزدیک | نظم‌دهی اطلاعات | استدلال استقرایی | روانی ایده‌ها | دید دور | انعطاف‌پذیری دسته‌بندی | اصالت | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | تشخیص گفتار | درک کتبی | بیان کتبی | استدلال قیاسی | حساسیت به مسئله | بینایی نزدیک | ترتیب‌دهی اطلاعات | استدلال استقرایی | روانی ایده‌ها | بینایی دور | انعطاف‌پذیری دسته‌بندی | اصالت | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | تعامل با مشتریان خارجی یا عموم مردم | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل محیطی | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سخنرانی عمومی | فضای باز، در معرض تمام شرایط آب و هوایی | آزادی در تصمیم‌گیری | محیط داخلی، بدون کنترل محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>ایمیل | تعامل با مشتریان خارجی یا عموم مردم | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سخنرانی عمومی | فضای باز، در معرض تمام شرایط آب و هوایی | آزادی در تصمیم‌گیری | محیط داخلی، بدون کنترل شرایط محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>دانشمندان حفاظت | مدیران آموزش و مراقبت از کودک، پیش‌دبستانی و مهدکودک | مدیران سرگرمی و تفریح، به جز قمار | برنامه‌ریزان احیای محیط زیست | معلمان علوم محیطی، پس از متوسطه | دانشمندان و متخصصان محیط زیست، شامل بهداشت | سرپرستان خط اول کارکنان سرگرمی و تفریح، به جز خدمات قمار | محیط‌بانان ماهی و شکار | بازرسان و متخصصان پیشگیری از آتش‌سوزی جنگل | تکنیسین‌های جنگل و حفاظت | کارکنان جنگل و حفاظت | جنگل‌بانان | معلمان علوم جنگلداری و حفاظت، پس از متوسطه | جغرافیدان‌ها | تاریخ‌دان‌ها | هماهنگ‌کنندگان آموزشی | مدیران مراتع | کارکنان تفریحی | راهنمایان تور و همراهان | جانورشناسان و زیست‌شناسان حیات وحش</t>
+          <t>دانشمندان حفاظت | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | مدیران سرگرمی و تفریح، به جز قماربازی | برنامه‌ریزان احیای محیط‌زیست | مدرسان علوم محیطی، پس از متوسطه | دانشمندان و متخصصان محیط زیست، شامل بهداشت | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | محیط‌بانان و جنگل‌بانان | بازرسان و متخصصان پیشگیری از آتش‌سوزی جنگل | تکنسین‌های جنگل و حفاظت | کارگران جنگل و حفاظت | جنگل‌بانان | مدرسان علوم جنگلداری و حفاظت، پس از متوسطه | جغرافیدانان | مورخان | هماهنگ‌کنندگان آموزشی | مدیران مراتع | کارکنان تفریحات | راهنمایان تور و همراهان | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0022_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0022_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>علوم پایه | درک مطلب | تفکر انتقادی | نگارش | شنیدن فعال | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
+          <t>علوم | درک مطلب | تفکر انتقادی | نگارش | گوش دادن فعال | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | شیمی | زبان انگلیسی | رایانه و الکترونیک | آموزش و تدریس | ریاضیات | مهندسی و فناوری</t>
+          <t>زیست‌شناسی | شیمی | زبان انگلیسی | رایانه و الکترونیک | آموزش و پرورش | ریاضیات | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان کتبی | استدلال استقرایی | حساسیت به مسئله | استدلال قیاسی | انعطاف‌پذیری در طبقه‌بندی | درک شفاهی | بیان شفاهی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در ادراک الگوها | دید نزدیک | روانی کلام و ایده | تشخیص گفتار | توجه انتخابی | اصالت و ابتکار | وضوح گفتار | تشخیص تمایز رنگ‌ها | چابکی انگشتان | تجسم فضایی | سرعت ادراک</t>
+          <t>درک کتبی | بیان کتبی | استدلال استقرایی | حساسیت به مسئله | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | درک شفاهی | بیان شفاهی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | بینایی نزدیک | روانی ایده‌ها | تشخیص گفتار | توجه انتخابی | اصالت | وضوح گفتار | تشخیص رنگ بصری | مهارت انگشتان | تجسم | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تکنسین‌های کشاورزی | بیوشیمیست‌ها و بیوفیزیکدان‌ها | مهندسان زیستی و مهندسان پزشکی | متخصصان بیوانفورماتیک | تکنسین‌های زیست‌شناسی | زیست‌شناسان | تکنسین‌های شیمی | شیمیدان‌ها | تکنولوژیست‌های سیتوژنتیک | اپیدمیولوژیست‌ها | متخصصان ژنتیک | تکنسین‌های بافت‌شناسی | تکنولوژیست‌های بافت‌شناسی | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | تکنسین‌های آزمایشگاه پزشکی و بالینی | کارشناسان آزمایشگاه پزشکی و بالینی | زیست‌شناسان سلولی و مولکولی | تکنسین‌ها و تکنولوژیست‌های مهندسی نانوفناوری | پزشکان متخصص آسیب‌شناسی (پاتولوژیست‌ها) | دانشمندان خاک‌شناسی و علوم گیاهی</t>
+          <t>تکنسین‌های کشاورزی | زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | مهندسان پزشکی و بیوانجینیرینگ | متخصصان بیوانفورماتیک | تکنسین‌های علوم زیستی | زیست‌شناسان | تکنسین‌های شیمی | شیمی‌دانان | کارشناسان سیتوژنتیک | متخصصان همه‌گیرشناسی و اپیدمیولوژیست‌ها | متخصصان ژنتیک | کاردان‌های پاتولوژی و بافت‌شناسی | هیستوتکنولوژیست‌ها / کارشناسان بافت‌شناسی | پژوهشگران و دانشمندان علوم پزشکی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | زیست‌شناسان سلولی و مولکولی | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | پزشکان متخصص پاتولوژی | متخصصان خاک‌شناسی و علوم گیاهی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | علوم پایه | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | علوم | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | ریاضیات | جغرافیا | حقوق و مقررات دولتی | مدیریت و امور اداری | ارتباطات و رسانه</t>
+          <t>زیست‌شناسی | زبان انگلیسی | خدمات مشتری و شخصی | ریاضیات | جغرافیا | قانون و دولت | مدیریت و اداره | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | وضوح گفتار | مرتب‌سازی اطلاعات | حساسیت به مسئله | تشخیص گفتار | دید نزدیک | انعطاف‌پذیری در طبقه‌بندی | روانی کلام و ایده | اصالت و ابتکار | توجه انتخابی | انعطاف‌پذیری در ادراک الگوها | تقسیم توجه | سرعت ادراک | محاسبات عددی | استدلال ریاضی | دید دور</t>
+          <t>بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | وضوح گفتار | ترتیب‌دهی اطلاعات | حساسیت به مسئله | تشخیص گفتار | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | انعطاف‌پذیری بستار | تقسیم توجه | سرعت ادراکی | توانایی عددی | استدلال ریاضی | بینایی دور</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>استادان علوم کشاورزی دانشگاه‌ها و مراکز آموزش عالی | تکنسین‌های کشاورزی | متخصصان علوم دامی | تکنسین‌های زیست‌شناسی | زیست‌شناسان | دانشمندان حفاظت از منابع طبیعی | برنامه‌ریزان احیای محیط زیست | استادان علوم محیطی دانشگاه‌ها و مراکز آموزش عالی | دانشمندان و متخصصان محیط زیست، از جمله بهداشت محیط | محیط‌بانان و حافظان شیلات و حیات وحش | تکنسین‌های جنگلداری و حفاظت از منابع طبیعی | کارگران جنگلداری و حفاظت از منابع طبیعی | جنگلداران | استادان علوم جنگلداری و حفاظت منابع طبیعی دانشگاه‌ها و مراکز آموزش عالی | دانشمندان علوم زمین، به جز هیدرولوژیست‌ها و جغرافیدان‌ها | هیدرولوژیست‌ها (آب‌شناسان) | بوم‌شناسان صنعتی | میکروبیولوژیست‌ها | مدیران مراتع | دانشمندان خاک‌شناسی و علوم گیاهی</t>
+          <t>استادان و مدرسان علوم کشاورزی در دانشگاه‌ها و مراکز آموزش عالی | تکنسین‌های کشاورزی | متخصصان علوم دامی | تکنسین‌های علوم زیستی | زیست‌شناسان | دانشمندان حفاظت از منابع طبیعی | برنامه‌ریزان احیای محیط زیست | استادان و مدرسان علوم محیط‌زیست در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | محیط‌بانان و ماموران حفاظت شیلات و حیات وحش | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارگران جنگل‌داری و حفاظت از منابع طبیعی | کارشناسان جنگل‌داری و جنگل‌بانان | استادان و مدرسان جنگلداری و منابع طبیعی در دانشگاه‌ها و مراکز آموزش عالی | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | آب‌شناسان و هیدرولوژیست‌ها | بوم‌شناسان صنعتی | میکروبیولوژیست‌ها | مدیران و کارشناسان مدیریت مراتع | متخصصان خاک‌شناسی و علوم گیاهی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | شنیدن فعال | علوم پایه | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | شیمی | ریاضیات | زبان انگلیسی | رایانه و الکترونیک | آموزش و تدریس | فیزیک | مدیریت و امور اداری | پزشکی و دندانپزشکی</t>
+          <t>زیست‌شناسی | شیمی | ریاضیات | زبان انگلیسی | رایانه و الکترونیک | آموزش و پرورش | فیزیک | مدیریت و اداره | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | روانی کلام و ایده | اصالت و ابتکار | توجه انتخابی | تقسیم توجه | تجسم فضایی | حافظه | استدلال ریاضی | محاسبات عددی | سرعت ادراک | انعطاف‌پذیری در ادراک الگوها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>جانورشناسان و زیست‌شناسان حیات وحش | میکروبیولوژیست‌ها | بیوشیمیست‌ها و بیوفیزیکدان‌ها | زیست‌شناسان سلولی و مولکولی | متخصصان ژنتیک | زیست‌شناسان | متخصصان بیوانفورماتیک | متخصصان علوم دامی | دانشمندان خاک‌شناسی و علوم گیاهی | دانشمندان و کارشناسان علوم و صنایع غذایی | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | اپیدمیولوژیست‌ها | دانشمندان حفاظت از منابع طبیعی | جنگلداران | دانشمندان و متخصصان محیط زیست، از جمله بهداشت محیط | تکنسین‌های زیست‌شناسی | استادان علوم زیستی دانشگاه‌ها و مراکز آموزش عالی | مدیران علوم طبیعی | مدیران مراتع | طبیعت‌شناسان پارک‌های ملی و طبیعی</t>
+          <t>جانورشناسان و زیست‌شناسان حیات وحش | میکروبیولوژیست‌ها | زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | زیست‌شناسان سلولی و مولکولی | متخصصان ژنتیک | زیست‌شناسان | متخصصان بیوانفورماتیک | متخصصان علوم دامی | متخصصان خاک‌شناسی و علوم گیاهی | متخصصان و کارشناسان علوم و صنایع غذایی | پژوهشگران و دانشمندان علوم پزشکی | متخصصان همه‌گیرشناسی و اپیدمیولوژیست‌ها | دانشمندان حفاظت از منابع طبیعی | کارشناسان جنگل‌داری و جنگل‌بانان | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | تکنسین‌های علوم زیستی | استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | مدیران علوم طبیعی و پایه‌ای | مدیران و کارشناسان مدیریت مراتع | طبیعت‌شناسان و کارشناسان پارک‌های ملی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | سخن گفتن | شنیدن فعال | نگارش | علوم پایه | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | درک مطلب | سخن گفتن | گوش دادن فعال | نگارش | علوم | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | رایانه و الکترونیک | ریاضیات | زبان انگلیسی | شیمی | آموزش و تدریس | امور دفتری و اداری</t>
+          <t>زیست‌شناسی | رایانه و الکترونیک | ریاضیات | زبان انگلیسی | شیمی | آموزش و پرورش | اداری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | روانی کلام و ایده | استدلال ریاضی | اصالت و ابتکار | انعطاف‌پذیری در طبقه‌بندی | دید نزدیک | محاسبات عددی | وضوح گفتار | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری در ادراک الگوها | دید دور | سرعت ادراک | حافظه</t>
+          <t>بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | استدلال ریاضی | اصالت | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | توانایی عددی | وضوح گفتار | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری بستار | بینایی دور | سرعت ادراکی | حفظ کردن</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>بیوشیمیست‌ها و بیوفیزیکدان‌ها | مهندسان زیستی و مهندسان پزشکی | تکنسین‌های بیوانفورماتیک | استادان علوم زیستی دانشگاه‌ها و مراکز آموزش عالی | تکنسین‌های زیست‌شناسی | متخصصان آمار زیستی | مدیران داده‌های بالینی | تکنولوژیست‌های سیتوژنتیک | دانشمندان علوم داده | متخصصان ژنتیک | ریاضیدان‌ها | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | کارشناسان آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | زیست‌شناسان سلولی و مولکولی | مهندسان نانوسیستم | تکنسین‌ها و تکنولوژیست‌های مهندسی نانوفناوری | مدیران علوم طبیعی | توسعه‌دهندگان نرم‌افزار | کارشناسان آمار</t>
+          <t>زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | مهندسان پزشکی و بیوانجینیرینگ | تکنسین‌های بیوانفورماتیک | استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | تکنسین‌های علوم زیستی | کارشناسان آمار زیستی | مدیران داده‌های بالینی | کارشناسان سیتوژنتیک | دانشمندان داده | متخصصان ژنتیک | ریاضی‌دانان | پژوهشگران و دانشمندان علوم پزشکی | کارشناسان علوم آزمایشگاهی بالینی | میکروبیولوژیست‌ها | زیست‌شناسان سلولی و مولکولی | مهندسان نانوسیستم‌ها | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | مدیران علوم طبیعی و پایه‌ای | توسعه‌دهندگان نرم‌افزار | کارشناسان آمار</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>علوم پایه | درک مطلب | نگارش | تفکر انتقادی | سخن گفتن | شنیدن فعال | یادگیری فعال | راهبردهای یادگیری | ریاضیات | نظارت</t>
+          <t>علوم | درک مطلب | نگارش | تفکر انتقادی | سخن گفتن | گوش دادن فعال | یادگیری فعال | راهبردهای یادگیری | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | زبان انگلیسی | شیمی | ریاضیات | آموزش و تدریس | رایانه و الکترونیک | پزشکی و دندانپزشکی</t>
+          <t>زیست‌شناسی | زبان انگلیسی | شیمی | ریاضیات | آموزش و پرورش | رایانه و الکترونیک | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | استدلال استقرایی | حساسیت به مسئله | استدلال قیاسی | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال ریاضی | روانی کلام و ایده | دید نزدیک | وضوح گفتار | اصالت و ابتکار | تشخیص گفتار | محاسبات عددی | انعطاف‌پذیری در ادراک الگوها | توجه انتخابی | دید دور | سرعت ادراک | توانایی تشخیص سریع الگوها | تشخیص تمایز رنگ‌ها</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | استدلال استقرایی | حساسیت به مسئله | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال ریاضی | روانی ایده‌ها | بینایی نزدیک | وضوح گفتار | اصالت | تشخیص گفتار | توانایی عددی | انعطاف‌پذیری بستار | توجه انتخابی | بینایی دور | سرعت ادراکی | سرعت بستار | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>بیوشیمیست‌ها و بیوفیزیکدان‌ها | مهندسان زیستی و مهندسان پزشکی | متخصصان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | استادان علوم زیستی دانشگاه‌ها و مراکز آموزش عالی | تکنسین‌های زیست‌شناسی | زیست‌شناسان | استادان شیمی دانشگاه‌ها و مراکز آموزش عالی | شیمیدان‌ها | تکنولوژیست‌های سیتوژنتیک | متخصصان ژنتیک | تکنولوژیست‌های بافت‌شناسی | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | تکنسین‌های آزمایشگاه پزشکی و بالینی | کارشناسان آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | مهندسان نانوسیستم | تکنسین‌ها و تکنولوژیست‌های مهندسی نانوفناوری | مدیران علوم طبیعی | پزشکان متخصص آسیب‌شناسی (پاتولوژیست‌ها)</t>
+          <t>زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | مهندسان پزشکی و بیوانجینیرینگ | متخصصان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | تکنسین‌های علوم زیستی | زیست‌شناسان | استادان و مدرسان شیمی در دانشگاه‌ها و مراکز آموزش عالی | شیمی‌دانان | کارشناسان سیتوژنتیک | متخصصان ژنتیک | هیستوتکنولوژیست‌ها / کارشناسان بافت‌شناسی | پژوهشگران و دانشمندان علوم پزشکی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | میکروبیولوژیست‌ها | مهندسان نانوسیستم‌ها | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | مدیران علوم طبیعی و پایه‌ای | پزشکان متخصص پاتولوژی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | علوم پایه | یادگیری فعال | تفکر انتقادی | سخن گفتن | نگارش | شنیدن فعال | ریاضیات | راهبردهای یادگیری | نظارت</t>
+          <t>درک مطلب | علوم | یادگیری فعال | تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال | ریاضیات | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | زبان انگلیسی | آموزش و تدریس | ریاضیات | شیمی | رایانه و الکترونیک</t>
+          <t>زیست‌شناسی | زبان انگلیسی | آموزش و پرورش | ریاضیات | شیمی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان کتبی | استدلال استقرایی | بیان شفاهی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال ریاضی | روانی کلام و ایده | دید نزدیک | وضوح گفتار | اصالت و ابتکار | محاسبات عددی | انعطاف‌پذیری در ادراک الگوها | تشخیص گفتار | توجه انتخابی | دید دور</t>
+          <t>درک کتبی | بیان کتبی | استدلال استقرایی | بیان شفاهی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال ریاضی | روانی ایده‌ها | بینایی نزدیک | وضوح گفتار | اصالت | توانایی عددی | انعطاف‌پذیری بستار | تشخیص گفتار | توجه انتخابی | بینایی دور</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>بیوشیمیست‌ها و بیوفیزیکدان‌ها | مهندسان زیستی و مهندسان پزشکی | متخصصان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | استادان علوم زیستی دانشگاه‌ها و مراکز آموزش عالی | تکنسین‌های زیست‌شناسی | زیست‌شناسان | متخصصان آمار زیستی | هماهنگ‌کنندگان کارآزمایی‌های بالینی | تکنولوژیست‌های سیتوژنتیک | دانشمندان علوم داده | اپیدمیولوژیست‌ها | مشاوران ژنتیک | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | تکنسین‌های آزمایشگاه پزشکی و بالینی | کارشناسان آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | زیست‌شناسان سلولی و مولکولی | پزشکان متخصص آسیب‌شناسی (پاتولوژیست‌ها) | کارشناسان آمار</t>
+          <t>زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | مهندسان پزشکی و بیوانجینیرینگ | متخصصان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | تکنسین‌های علوم زیستی | زیست‌شناسان | کارشناسان آمار زیستی | هماهنگ‌کنندگان کارآزمایی‌های بالینی | کارشناسان سیتوژنتیک | دانشمندان داده | متخصصان همه‌گیرشناسی و اپیدمیولوژیست‌ها | مشاوران ژنتیک | پژوهشگران و دانشمندان علوم پزشکی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | میکروبیولوژیست‌ها | زیست‌شناسان سلولی و مولکولی | پزشکان متخصص پاتولوژی | کارشناسان آمار</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>علوم پایه | درک مطلب | نگارش | شنیدن فعال | تفکر انتقادی | سخن گفتن | ریاضیات | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
+          <t>علوم | درک مطلب | نگارش | گوش دادن فعال | تفکر انتقادی | سخن گفتن | ریاضیات | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | آموزش و تدریس | زبان انگلیسی | ریاضیات | مدیریت و امور اداری | شیمی | امور دفتری و اداری | مهندسی و فناوری | ارتباطات و رسانه</t>
+          <t>زیست‌شناسی | آموزش و پرورش | زبان انگلیسی | ریاضیات | مدیریت و اداره | شیمی | اداری | مهندسی و فناوری | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان کتبی | استدلال استقرایی | دید نزدیک | بیان شفاهی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | استدلال ریاضی | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | روانی کلام و ایده | انعطاف‌پذیری در ادراک الگوها | دید دور | محاسبات عددی | اصالت و ابتکار | تجسم فضایی | سرعت ادراک | تشخیص تمایز رنگ‌ها | توجه انتخابی</t>
+          <t>درک شفاهی | درک کتبی | بیان کتبی | استدلال استقرایی | بینایی نزدیک | بیان شفاهی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | روانی ایده‌ها | انعطاف‌پذیری بستار | بینایی دور | توانایی عددی | اصالت | تجسم | سرعت ادراکی | تشخیص رنگ بصری | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>بیوشیمیست‌ها و بیوفیزیکدان‌ها | مهندسان زیستی و مهندسان پزشکی | متخصصان بیوانفورماتیک | استادان علوم زیستی دانشگاه‌ها و مراکز آموزش عالی | تکنسین‌های زیست‌شناسی | دانشمندان حفاظت از منابع طبیعی | برنامه‌ریزان احیای محیط زیست | استادان علوم محیطی دانشگاه‌ها و مراکز آموزش عالی | دانشمندان و متخصصان محیط زیست، از جمله بهداشت محیط | استادان علوم جنگلداری و حفاظت منابع طبیعی دانشگاه‌ها و مراکز آموزش عالی | متخصصان ژنتیک | دانشمندان علوم زمین، به جز هیدرولوژیست‌ها و جغرافیدان‌ها | بوم‌شناسان صنعتی | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | کارشناسان آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | زیست‌شناسان سلولی و مولکولی | مدیران علوم طبیعی | دانشمندان خاک‌شناسی و علوم گیاهی | جانورشناسان و زیست‌شناسان حیات وحش</t>
+          <t>زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | مهندسان پزشکی و بیوانجینیرینگ | متخصصان بیوانفورماتیک | استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | تکنسین‌های علوم زیستی | دانشمندان حفاظت از منابع طبیعی | برنامه‌ریزان احیای محیط زیست | استادان و مدرسان علوم محیط‌زیست در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | استادان و مدرسان جنگلداری و منابع طبیعی در دانشگاه‌ها و مراکز آموزش عالی | متخصصان ژنتیک | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | بوم‌شناسان صنعتی | پژوهشگران و دانشمندان علوم پزشکی | کارشناسان علوم آزمایشگاهی بالینی | میکروبیولوژیست‌ها | زیست‌شناسان سلولی و مولکولی | مدیران علوم طبیعی و پایه‌ای | متخصصان خاک‌شناسی و علوم گیاهی | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | نگارش | علوم پایه | تفکر انتقادی | نظارت | یادگیری فعال | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | علوم | تفکر انتقادی | نظارت | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | زیست‌شناسی | جغرافیا | ریاضیات | خدمات مشتریان و خدمات فردی | شیمی | حقوق و مقررات دولتی | رایانه و الکترونیک | مهندسی و فناوری | آموزش و تدریس | طراحی | فیزیک | مدیریت و امور اداری</t>
+          <t>زبان انگلیسی | زیست‌شناسی | جغرافیا | ریاضیات | خدمات مشتری و شخصی | شیمی | قانون و دولت | رایانه و الکترونیک | مهندسی و فناوری | آموزش و پرورش | طراحی | فیزیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | بیان کتبی | استدلال استقرایی | وضوح گفتار | انعطاف‌پذیری در ادراک الگوها | دید نزدیک | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | روانی کلام و ایده | اصالت و ابتکار | استدلال ریاضی | محاسبات عددی | دید دور | سرعت ادراک</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | بیان کتبی | استدلال استقرایی | وضوح گفتار | انعطاف‌پذیری بستار | بینایی نزدیک | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | استدلال ریاضی | توانایی عددی | بینایی دور | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | زیست‌شناسان | متخصصان احیای اراضی قهوه‌ای و مدیران سایت | بازرسان انطباق زیست‌محیطی | مهندسان محیط زیست | برنامه‌ریزان احیای محیط زیست | تکنسین‌های حفاظت و علوم محیطی، از جمله بهداشت | دانشمندان و متخصصان محیط زیست، از جمله بهداشت محیط | تکنسین‌های جنگلداری و حفاظت از منابع طبیعی | جنگلداران | دانشمندان علوم زمین، به جز هیدرولوژیست‌ها و جغرافیدان‌ها | تکنسین‌های هیدرولوژی | هیدرولوژیست‌ها (آب‌شناسان) | بوم‌شناسان صنعتی | طبیعت‌شناسان پارک‌های ملی و طبیعی | مدیران مراتع | دانشمندان خاک‌شناسی و علوم گیاهی | متخصصان منابع آب | مهندسان آب و فاضلاب | جانورشناسان و زیست‌شناسان حیات وحش</t>
+          <t>مهندسان کشاورزی | زیست‌شناسان | مدیران و کارشناسان احیا و بازسازی اراضی قهوه‌ای و آلوده | بازرسان رعایت ضوابط زیست‌محیطی | مهندسان محیط‌زیست | برنامه‌ریزان احیای محیط زیست | تکنسین‌های علوم و بهداشت محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارشناسان جنگل‌داری و جنگل‌بانان | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | تکنسین‌های آب‌شناسی و هیدرولوژی | آب‌شناسان و هیدرولوژیست‌ها | بوم‌شناسان صنعتی | طبیعت‌شناسان و کارشناسان پارک‌های ملی | مدیران و کارشناسان مدیریت مراتع | متخصصان خاک‌شناسی و علوم گیاهی | کارشناسان و متخصصان مدیریت منابع آب | مهندسان آب و فاضلاب | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | نگارش</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | زبان انگلیسی | جغرافیا | حقوق و مقررات دولتی | مدیریت و امور اداری | امور دفتری و اداری | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | رایانه و الکترونیک | آموزش و تدریس | ریاضیات | طراحی</t>
+          <t>زیست‌شناسی | زبان انگلیسی | جغرافیا | قانون و دولت | مدیریت و اداره | اداری | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | رایانه و الکترونیک | آموزش و پرورش | ریاضیات | طراحی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان شفاهی | درک شفاهی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | استدلال قیاسی | دید نزدیک | وضوح گفتار | تشخیص گفتار | دید دور | مرتب‌سازی اطلاعات | روانی کلام و ایده | اصالت و ابتکار | انعطاف‌پذیری در طبقه‌بندی | توجه انتخابی | انعطاف‌پذیری در ادراک الگوها | استدلال ریاضی</t>
+          <t>درک کتبی | بیان شفاهی | درک شفاهی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | استدلال قیاسی | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | بینایی دور | ترتیب‌دهی اطلاعات | روانی ایده‌ها | اصالت | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | انعطاف‌پذیری بستار | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | زیست‌شناسان | متخصصان احیای اراضی قهوه‌ای و مدیران سایت | مدیران ارشد پایداری سازمانی | دانشمندان حفاظت از منابع طبیعی | مهندسان محیط زیست | برنامه‌ریزان احیای محیط زیست | دانشمندان و متخصصان محیط زیست، از جمله بهداشت محیط | سرپرستان رده‌اول کارگران کشاورزی، صیادی و جنگلداری | محیط‌بانان و حافظان شیلات و حیات وحش | بازرسان و کارشناسان پیشگیری و اطفای حریق جنگل | تکنسین‌های جنگلداری و حفاظت از منابع طبیعی | کارگران جنگلداری و حفاظت از منابع طبیعی | جنگلداران | تکنسین‌های هیدرولوژی | بوم‌شناسان صنعتی | طبیعت‌شناسان پارک‌های ملی و طبیعی | دانشمندان خاک‌شناسی و علوم گیاهی | متخصصان منابع آب | جانورشناسان و زیست‌شناسان حیات وحش</t>
+          <t>مهندسان کشاورزی | زیست‌شناسان | مدیران و کارشناسان احیا و بازسازی اراضی قهوه‌ای و آلوده | مدیران ارشد پایداری سازمانی | دانشمندان حفاظت از منابع طبیعی | مهندسان محیط‌زیست | برنامه‌ریزان احیای محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | محیط‌بانان و ماموران حفاظت شیلات و حیات وحش | بازرسان و کارشناسان پیشگیری از حریق جنگل | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارگران جنگل‌داری و حفاظت از منابع طبیعی | کارشناسان جنگل‌داری و جنگل‌بانان | تکنسین‌های آب‌شناسی و هیدرولوژی | بوم‌شناسان صنعتی | طبیعت‌شناسان و کارشناسان پارک‌های ملی | متخصصان خاک‌شناسی و علوم گیاهی | کارشناسان و متخصصان مدیریت منابع آب | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | شنیدن فعال | نگارش | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | آموزش و تدریس | زبان انگلیسی | ایمنی و امنیت عمومی | زیست‌شناسی | ارتباطات و رسانه | تاریخ و باستان‌شناسی | حقوق و مقررات دولتی | جغرافیا</t>
+          <t>خدمات مشتری و شخصی | آموزش و پرورش | زبان انگلیسی | ایمنی و امنیت عمومی | زیست‌شناسی | ارتباطات و رسانه | تاریخ و باستان‌شناسی | قانون و دولت | جغرافیا</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | تشخیص گفتار | درک کتبی | بیان کتبی | استدلال قیاسی | حساسیت به مسئله | دید نزدیک | مرتب‌سازی اطلاعات | استدلال استقرایی | روانی کلام و ایده | دید دور | انعطاف‌پذیری در طبقه‌بندی | اصالت و ابتکار | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری در ادراک الگوها</t>
+          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | تشخیص گفتار | درک کتبی | بیان کتبی | استدلال قیاسی | حساسیت به مسئله | بینایی نزدیک | ترتیب‌دهی اطلاعات | استدلال استقرایی | روانی ایده‌ها | بینایی دور | انعطاف‌پذیری دسته‌بندی | اصالت | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>دانشمندان حفاظت از منابع طبیعی | مدیران آموزشی و مراکز مراقبت از کودکان | مدیران مراکز تفریحی و سرگرمی، به جز قمار | برنامه‌ریزان احیای محیط زیست | استادان علوم محیطی دانشگاه‌ها و مراکز آموزش عالی | دانشمندان و متخصصان محیط زیست، از جمله بهداشت محیط | سرپرستان رده‌اول کارکنان سرگرمی و تفریحی | محیط‌بانان و حافظان شیلات و حیات وحش | بازرسان و کارشناسان پیشگیری و اطفای حریق جنگل | تکنسین‌های جنگلداری و حفاظت از منابع طبیعی | کارگران جنگلداری و حفاظت از منابع طبیعی | جنگلداران | استادان علوم جنگلداری و حفاظت منابع طبیعی دانشگاه‌ها و مراکز آموزش عالی | جغرافیدان‌ها | تاریخ‌نگاران (مورخان) | هماهنگ‌کنندگان آموزشی و تدوین برنامه‌های درسی | مدیران مراتع | کارکنان خدمات تفریحی و اوقات فراغت | راهنمایان تور و گردشگری | جانورشناسان و زیست‌شناسان حیات وحش</t>
+          <t>دانشمندان حفاظت از منابع طبیعی | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | مدیران مجموعه‌های تفریحی، ورزشی و رویدادها | برنامه‌ریزان احیای محیط زیست | استادان و مدرسان علوم محیط‌زیست در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | محیط‌بانان و ماموران حفاظت شیلات و حیات وحش | بازرسان و کارشناسان پیشگیری از حریق جنگل | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارگران جنگل‌داری و حفاظت از منابع طبیعی | کارشناسان جنگل‌داری و جنگل‌بانان | استادان و مدرسان جنگلداری و منابع طبیعی در دانشگاه‌ها و مراکز آموزش عالی | جغرافیدانان | مورخان | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مدیران و کارشناسان مدیریت مراتع | کارکنان و متصدیان امور تفریحی و اوقات فراغت | راهنمایان تور و گردشگری | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
